--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Migración interna neta</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:21</t>
+    <t xml:space="preserve">2026-07-30 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_miginterna_a_2021.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Migracion interna neta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2021.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">Magallanes</t>
@@ -298,18 +298,18 @@
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
     <t xml:space="preserve">13302</t>
   </si>
   <si>
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
-    <t xml:space="preserve">5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
     <t xml:space="preserve">7403</t>
   </si>
   <si>
@@ -328,18 +328,18 @@
     <t xml:space="preserve">La Ligua</t>
   </si>
   <si>
+    <t xml:space="preserve">5606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
     <t xml:space="preserve">6107</t>
   </si>
   <si>
     <t xml:space="preserve">Las Cabras</t>
   </si>
   <si>
-    <t xml:space="preserve">5606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
     <t xml:space="preserve">13130</t>
   </si>
   <si>
@@ -418,18 +418,18 @@
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
+    <t xml:space="preserve">5101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">13604</t>
   </si>
   <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">5101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">6108</t>
   </si>
   <si>
@@ -526,34 +526,40 @@
     <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
+    <t xml:space="preserve">5504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
     <t xml:space="preserve">6302</t>
   </si>
   <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
-    <t xml:space="preserve">5504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
     <t xml:space="preserve">13120</t>
   </si>
   <si>
     <t xml:space="preserve">Ñuñoa</t>
   </si>
   <si>
+    <t xml:space="preserve">13301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
     <t xml:space="preserve">6105</t>
   </si>
   <si>
     <t xml:space="preserve">Doñihue</t>
   </si>
   <si>
-    <t xml:space="preserve">13301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
+    <t xml:space="preserve">13603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
     <t xml:space="preserve">7109</t>
@@ -562,12 +568,6 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
-    <t xml:space="preserve">13603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">7106</t>
   </si>
   <si>
@@ -673,36 +673,36 @@
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">7407</t>
   </si>
   <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">5304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">6310</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">13129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
     <t xml:space="preserve">6111</t>
   </si>
   <si>
     <t xml:space="preserve">Olivar</t>
   </si>
   <si>
-    <t xml:space="preserve">13129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
     <t xml:space="preserve">5706</t>
   </si>
   <si>
@@ -793,18 +793,18 @@
     <t xml:space="preserve">Requínoa</t>
   </si>
   <si>
+    <t xml:space="preserve">13110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
     <t xml:space="preserve">6301</t>
   </si>
   <si>
     <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
-    <t xml:space="preserve">13110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
     <t xml:space="preserve">7301</t>
   </si>
   <si>
@@ -955,18 +955,18 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">13303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
     <t xml:space="preserve">16304</t>
   </si>
   <si>
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">13303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
     <t xml:space="preserve">13131</t>
   </si>
   <si>
@@ -1768,18 +1768,18 @@
     <t xml:space="preserve">Curaco de Vélez</t>
   </si>
   <si>
+    <t xml:space="preserve">8301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">9105</t>
   </si>
   <si>
     <t xml:space="preserve">Freire</t>
   </si>
   <si>
-    <t xml:space="preserve">8301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
     <t xml:space="preserve">9118</t>
   </si>
   <si>
@@ -1987,18 +1987,18 @@
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
+    <t xml:space="preserve">9107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorbea</t>
+  </si>
+  <si>
     <t xml:space="preserve">10404</t>
   </si>
   <si>
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">9107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorbea</t>
-  </si>
-  <si>
     <t xml:space="preserve">9111</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:28</t>
+    <t xml:space="preserve">2026-09-08 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3816,10 +3816,10 @@
         <v>2021</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>93</v>
@@ -3848,10 +3848,10 @@
         <v>2021</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>95</v>
@@ -3976,10 +3976,10 @@
         <v>2021</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>103</v>
@@ -4008,10 +4008,10 @@
         <v>2021</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>105</v>
@@ -4456,10 +4456,10 @@
         <v>2021</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>133</v>
@@ -4488,10 +4488,10 @@
         <v>2021</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>135</v>
@@ -5032,10 +5032,10 @@
         <v>2021</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>169</v>
@@ -5064,10 +5064,10 @@
         <v>2021</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>171</v>
@@ -5128,10 +5128,10 @@
         <v>2021</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>175</v>
@@ -5160,10 +5160,10 @@
         <v>2021</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>177</v>
@@ -5192,10 +5192,10 @@
         <v>2021</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>179</v>
@@ -5224,10 +5224,10 @@
         <v>2021</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>181</v>
@@ -5800,10 +5800,10 @@
         <v>2021</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>218</v>
@@ -5832,10 +5832,10 @@
         <v>2021</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>220</v>
@@ -5896,10 +5896,10 @@
         <v>2021</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>224</v>
@@ -5928,10 +5928,10 @@
         <v>2021</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>226</v>
@@ -6440,10 +6440,10 @@
         <v>2021</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>258</v>
@@ -6472,10 +6472,10 @@
         <v>2021</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>260</v>
@@ -7304,10 +7304,10 @@
         <v>2021</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>312</v>
@@ -7336,10 +7336,10 @@
         <v>2021</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>314</v>
@@ -11464,10 +11464,10 @@
         <v>2021</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>583</v>
@@ -11496,10 +11496,10 @@
         <v>2021</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>585</v>
@@ -12648,10 +12648,10 @@
         <v>2021</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>656</v>
@@ -12680,10 +12680,10 @@
         <v>2021</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>658</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
